--- a/tests/testthat/fixtures/ex2/tables/irt_poly.xlsx
+++ b/tests/testthat/fixtures/ex2/tables/irt_poly.xlsx
@@ -190,31 +190,31 @@
     <t xml:space="preserve">step3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67 (0.072)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.56 (0.072)</t>
+    <t xml:space="preserve">1.67 (0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.56 (0.07)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.11</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36 (0.072)</t>
+    <t xml:space="preserve">0.36 (0.07)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.36</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84 (0.082)</t>
+    <t xml:space="preserve">0.84 (0.08)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.84</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26 (0.082)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.96 (0.092)</t>
+    <t xml:space="preserve">1.26 (0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.96 (0.09)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.30</t>
